--- a/____Unpublished__CellProportions/CellProportions_summary_data.xlsx
+++ b/____Unpublished__CellProportions/CellProportions_summary_data.xlsx
@@ -676,8 +676,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="66af2654134d243f62aac8e2b322f1d6">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2bc3adf68671d86faa9c37249f400344" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d42a73f51a03135be35f4acb272f8cf1">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2ea21b36c10eaa86a5cb337ec7f4e0a6" ns2:_="" ns3:_="">
     <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
     <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
     <xsd:element name="properties">
@@ -701,6 +701,8 @@
                 <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -775,6 +777,16 @@
     <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
@@ -928,7 +940,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{795AE394-E89B-4B53-9CB5-1C777935A0BE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2E8A4699-C4FA-4B63-B418-9309A1F7683B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>

--- a/____Unpublished__CellProportions/CellProportions_summary_data.xlsx
+++ b/____Unpublished__CellProportions/CellProportions_summary_data.xlsx
@@ -1,21 +1,110 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10811"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alleninstitute.sharepoint.com/sites/MammalianM1/Shared Documents/General/Species/Evo-M1-Trait-Data/____Unpublished__CellProportions/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="6" documentId="11_04155E1FB24084EEB454E38CB4FD0D4EA7371550" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{09E72C8C-6259-9245-BCD1-8168BF396953}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="760" windowWidth="18740" windowHeight="16380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+  <si>
+    <t>Species_full</t>
+  </si>
+  <si>
+    <t>%NeuN+</t>
+  </si>
+  <si>
+    <t>%NeuN-</t>
+  </si>
+  <si>
+    <t>Aotus nancymaae</t>
+  </si>
+  <si>
+    <t>Canis latrans</t>
+  </si>
+  <si>
+    <t>Chlorocebus sabaeus</t>
+  </si>
+  <si>
+    <t>Dasypus novemcinctus</t>
+  </si>
+  <si>
+    <t>Felis catus</t>
+  </si>
+  <si>
+    <t>Gorilla gorilla</t>
+  </si>
+  <si>
+    <t>Heterocephalus glaber</t>
+  </si>
+  <si>
+    <t>Homo sapiens</t>
+  </si>
+  <si>
+    <t>Macaca mulatta</t>
+  </si>
+  <si>
+    <t>Macaca nemestrina</t>
+  </si>
+  <si>
+    <t>Microcebus murinus</t>
+  </si>
+  <si>
+    <t>Monodelphis domestica</t>
+  </si>
+  <si>
+    <t>Mustela putorius furo</t>
+  </si>
+  <si>
+    <t>Oryctolagus cuniculus</t>
+  </si>
+  <si>
+    <t>Otolemur garnettii</t>
+  </si>
+  <si>
+    <t>Pan troglodytes</t>
+  </si>
+  <si>
+    <t>Papio anubis</t>
+  </si>
+  <si>
+    <t>Rattus norvegicus</t>
+  </si>
+  <si>
+    <t>Saimiri sciureus</t>
+  </si>
+  <si>
+    <t>Sapajus apella</t>
+  </si>
+  <si>
+    <t>Sus scrofa</t>
+  </si>
+  <si>
+    <t>Tupaia belangeri</t>
+  </si>
+  <si>
+    <t>Urocitellus parryii</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,13 +152,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -107,7 +204,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -141,6 +238,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -175,9 +273,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -350,324 +449,275 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Species_full</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>%NeuN+</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>%NeuN-</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Aotus nancymaae</t>
-        </is>
+    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>3</v>
       </c>
       <c r="B2">
-        <v>0.468</v>
+        <v>0.46800000000000003</v>
       </c>
       <c r="C2">
-        <v>0.5243333333333333</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Canis latrans</t>
-        </is>
+        <v>0.52433333333333332</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>4</v>
       </c>
       <c r="B3">
-        <v>0.4633333333333333</v>
+        <v>0.46333333333333332</v>
       </c>
       <c r="C3">
-        <v>0.5263333333333333</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Chlorocebus sabaeus</t>
-        </is>
+        <v>0.52633333333333332</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>5</v>
       </c>
       <c r="B4">
-        <v>0.4905</v>
+        <v>0.49049999999999999</v>
       </c>
       <c r="C4">
-        <v>0.506</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Dasypus novemcinctus</t>
-        </is>
+        <v>0.50600000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>6</v>
       </c>
       <c r="B5">
-        <v>0.2377857142857143</v>
+        <v>0.23778571428571429</v>
       </c>
       <c r="C5">
-        <v>0.7570714285714286</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Felis catus</t>
-        </is>
+        <v>0.75707142857142862</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>7</v>
       </c>
       <c r="B6">
-        <v>0.6073999999999999</v>
+        <v>0.60739999999999994</v>
       </c>
       <c r="C6">
-        <v>0.3878</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Gorilla gorilla</t>
-        </is>
+        <v>0.38779999999999998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>8</v>
       </c>
       <c r="B7">
-        <v>0.3446666666666667</v>
+        <v>0.34466666666666668</v>
       </c>
       <c r="C7">
-        <v>0.644</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Heterocephalus glaber</t>
-        </is>
+        <v>0.64400000000000002</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>9</v>
       </c>
       <c r="B8">
         <v>0.66125</v>
       </c>
       <c r="C8">
-        <v>0.331</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Homo sapiens</t>
-        </is>
+        <v>0.33100000000000002</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>10</v>
       </c>
       <c r="B9">
-        <v>0.3081111111111111</v>
+        <v>0.30811111111111111</v>
       </c>
       <c r="C9">
         <v>0.6657777777777778</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Macaca mulatta</t>
-        </is>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>11</v>
       </c>
       <c r="B10">
-        <v>0.332375</v>
+        <v>0.33237499999999998</v>
       </c>
       <c r="C10">
-        <v>0.659125</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Macaca nemestrina</t>
-        </is>
+        <v>0.65912499999999996</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>12</v>
       </c>
       <c r="B11">
-        <v>0.334</v>
+        <v>0.33400000000000002</v>
       </c>
       <c r="C11">
-        <v>0.6640909090909091</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Microcebus murinus</t>
-        </is>
+        <v>0.66409090909090907</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>13</v>
       </c>
       <c r="B12">
-        <v>0.5213333333333333</v>
+        <v>0.52133333333333332</v>
       </c>
       <c r="C12">
-        <v>0.4473333333333333</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Monodelphis domestica</t>
-        </is>
+        <v>0.44733333333333331</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>14</v>
       </c>
       <c r="B13">
-        <v>0.5200625</v>
+        <v>0.52006249999999998</v>
       </c>
       <c r="C13">
-        <v>0.4461875</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Mustela putorius furo</t>
-        </is>
+        <v>0.44618750000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>15</v>
       </c>
       <c r="B14">
-        <v>0.5814166666666667</v>
+        <v>0.58141666666666669</v>
       </c>
       <c r="C14">
-        <v>0.4096666666666667</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Oryctolagus cuniculus</t>
-        </is>
+        <v>0.40966666666666668</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>16</v>
       </c>
       <c r="B15">
-        <v>0.360625</v>
+        <v>0.36062499999999997</v>
       </c>
       <c r="C15">
-        <v>0.632625</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Otolemur garnettii</t>
-        </is>
+        <v>0.63262499999999999</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>17</v>
       </c>
       <c r="B16">
-        <v>0.5278</v>
+        <v>0.52780000000000005</v>
       </c>
       <c r="C16">
-        <v>0.467</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Pan troglodytes</t>
-        </is>
+        <v>0.46700000000000003</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>18</v>
       </c>
       <c r="B17">
         <v>0.4087777777777778</v>
       </c>
       <c r="C17">
-        <v>0.5311111111111111</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Papio anubis</t>
-        </is>
+        <v>0.53111111111111109</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>19</v>
       </c>
       <c r="B18">
-        <v>0.3894444444444444</v>
+        <v>0.38944444444444443</v>
       </c>
       <c r="C18">
-        <v>0.6044444444444445</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Rattus norvegicus</t>
-        </is>
+        <v>0.60444444444444445</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>20</v>
       </c>
       <c r="B19">
-        <v>0.5367999999999999</v>
+        <v>0.53679999999999994</v>
       </c>
       <c r="C19">
-        <v>0.4505</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Saimiri sciureus</t>
-        </is>
+        <v>0.45050000000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>21</v>
       </c>
       <c r="B20">
-        <v>0.4634615384615385</v>
+        <v>0.46346153846153848</v>
       </c>
       <c r="C20">
-        <v>0.5343076923076923</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Sapajus apella</t>
-        </is>
+        <v>0.53430769230769226</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>22</v>
       </c>
       <c r="B21">
-        <v>0.3437777777777778</v>
+        <v>0.34377777777777779</v>
       </c>
       <c r="C21">
-        <v>0.6328888888888889</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Sus scrofa</t>
-        </is>
+        <v>0.63288888888888895</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>23</v>
       </c>
       <c r="B22">
-        <v>0.30175</v>
+        <v>0.30175000000000002</v>
       </c>
       <c r="C22">
-        <v>0.69575</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Tupaia belangeri</t>
-        </is>
+        <v>0.69574999999999998</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>24</v>
       </c>
       <c r="B23">
-        <v>0.4508571428571428</v>
+        <v>0.45085714285714279</v>
       </c>
       <c r="C23">
         <v>0.5326428571428572</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Urocitellus parryii</t>
-        </is>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>25</v>
       </c>
       <c r="B24">
-        <v>0.4744285714285714</v>
+        <v>0.47442857142857142</v>
       </c>
       <c r="C24">
-        <v>0.5227142857142857</v>
+        <v>0.52271428571428569</v>
       </c>
     </row>
   </sheetData>
@@ -676,6 +726,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d42a73f51a03135be35f4acb272f8cf1">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2ea21b36c10eaa86a5cb337ec7f4e0a6" ns2:_="" ns3:_="">
     <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
@@ -930,19 +989,29 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2E8A4699-C4FA-4B63-B418-9309A1F7683B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9DC321BD-CA24-4F86-B38D-BD9E2C5BC08D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9DC321BD-CA24-4F86-B38D-BD9E2C5BC08D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2E8A4699-C4FA-4B63-B418-9309A1F7683B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>